--- a/docs/project-task-list.xlsx
+++ b/docs/project-task-list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D00283071\Desktop\2 YEAR\Server-side Development\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711639AA-FCD9-46AF-90CB-5A751C329EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AB86A7-DD35-4011-82D1-8F27C85BCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
   <si>
     <t>Project Concept and Problem Statement</t>
   </si>
@@ -214,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -222,14 +222,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +518,7 @@
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
@@ -624,10 +623,10 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -637,10 +636,10 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,7 +656,7 @@
       <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="1"/>
@@ -697,7 +696,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -787,7 +786,7 @@
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D20" s="1"/>
@@ -799,7 +798,7 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="1"/>
@@ -810,18 +809,20 @@
       <c r="I21" s="1"/>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="1"/>
@@ -832,18 +833,20 @@
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D25" s="1"/>
@@ -854,7 +857,7 @@
       <c r="I25" s="1"/>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="1"/>
@@ -865,7 +868,7 @@
       <c r="I26" s="1"/>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D27" s="1"/>

--- a/docs/project-task-list.xlsx
+++ b/docs/project-task-list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H\WebstormProjects\task-planner\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AB86A7-DD35-4011-82D1-8F27C85BCABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E9B2EA-6B2D-4BC6-BE3C-914B4DD247FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>Project Concept and Problem Statement</t>
   </si>
@@ -817,7 +817,9 @@
         <v>15</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
@@ -841,7 +843,9 @@
         <v>15</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>

--- a/docs/project-task-list.xlsx
+++ b/docs/project-task-list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D00283071\Desktop\2 YEAR\Server-side Development\task-planner\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A766641-D030-4227-92BE-DECF098B1964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447510BD-E6C9-40F5-8D90-DD8BCB46E83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -945,7 +945,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="1"/>

--- a/docs/project-task-list.xlsx
+++ b/docs/project-task-list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D00283071\Desktop\2 YEAR\Server-side Development\task-planner\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447510BD-E6C9-40F5-8D90-DD8BCB46E83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465B26C2-E705-4D73-80D9-BC22253F3EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -832,11 +832,11 @@
         <v>23</v>
       </c>
       <c r="D20" s="1"/>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H20" s="1"/>
@@ -850,7 +850,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="1"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="3" t="s">
+      <c r="H21" s="2" t="s">
         <v>33</v>
       </c>
       <c r="I21" s="1"/>
@@ -863,7 +863,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="1"/>
@@ -873,11 +873,11 @@
         <v>25</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="1"/>
@@ -888,7 +888,7 @@
         <v>26</v>
       </c>
       <c r="D24" s="1"/>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="1"/>
@@ -901,11 +901,11 @@
         <v>27</v>
       </c>
       <c r="D25" s="1"/>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="1"/>
@@ -919,7 +919,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I26" s="1"/>
@@ -932,7 +932,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="1"/>
@@ -958,7 +958,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="H29" s="2"/>
       <c r="I29" s="1"/>
     </row>
   </sheetData>
